--- a/dashboard/assets/notas/acesso-2023.xlsx
+++ b/dashboard/assets/notas/acesso-2023.xlsx
@@ -1,173 +1,42 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Planilhas</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>7</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="7" baseType="lpstr">
-      <vt:lpstr>TOTAL</vt:lpstr>
-      <vt:lpstr>COREOGRAFIA</vt:lpstr>
-      <vt:lpstr>MARCAÇÃO</vt:lpstr>
-      <vt:lpstr>ANIMAÇÃO</vt:lpstr>
-      <vt:lpstr>FIGURINOS</vt:lpstr>
-      <vt:lpstr>CASAL DE NOIVOS</vt:lpstr>
-      <vt:lpstr>TRILHA SONORA</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\site-linq-dfe-beta\dashboard\assets\notas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1031D253-6BE7-4E87-8B70-408337EF884F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="TOTAL" sheetId="7" r:id="rId1"/>
+    <sheet name="COREOGRAFIA" sheetId="1" r:id="rId2"/>
+    <sheet name="MARCAÇÃO" sheetId="2" r:id="rId3"/>
+    <sheet name="ANIMAÇÃO" sheetId="3" r:id="rId4"/>
+    <sheet name="FIGURINOS" sheetId="4" r:id="rId5"/>
+    <sheet name="CASAL DE NOIVOS" sheetId="5" r:id="rId6"/>
+    <sheet name="TRILHA SONORA" sheetId="6" r:id="rId7"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>Tiago</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-12T20:35:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-15T11:05:39Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="Created">
-    <vt:filetime>2026-02-02T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="Creator">
-    <vt:lpwstr>www.smallpdf.com</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="LastSaved">
-    <vt:filetime>2026-03-12T00:00:00Z</vt:filetime>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="5" name="Producer">
-    <vt:lpwstr>www.smallpdf.com</vt:lpwstr>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
-<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <c r="G8" i="6" l="1"/>
-  <c r="H8" i="6" s="1"/>
-  <c r="G7" i="6"/>
-  <c r="H7" i="6" s="1"/>
-  <c r="G6" i="6"/>
-  <c r="H6" i="6" s="1"/>
-  <c r="G5" i="6"/>
-  <c r="H5" i="6" s="1"/>
-  <c r="G4" i="6"/>
-  <c r="H4" i="6" s="1"/>
-  <c r="H3" i="6"/>
-  <c r="G3" i="6"/>
-  <c r="G2" i="6"/>
-  <c r="H2" i="6" s="1"/>
-  <c r="G8" i="5"/>
-  <c r="H8" i="5" s="1"/>
-  <c r="G7" i="5"/>
-  <c r="H7" i="5" s="1"/>
-  <c r="G6" i="5"/>
-  <c r="H6" i="5" s="1"/>
-  <c r="G5" i="5"/>
-  <c r="H5" i="5" s="1"/>
-  <c r="G4" i="5"/>
-  <c r="H4" i="5" s="1"/>
-  <c r="G3" i="5"/>
-  <c r="H3" i="5" s="1"/>
-  <c r="G2" i="5"/>
-  <c r="H2" i="5" s="1"/>
-  <c r="G8" i="4"/>
-  <c r="H8" i="4" s="1"/>
-  <c r="G7" i="4"/>
-  <c r="H7" i="4" s="1"/>
-  <c r="G6" i="4"/>
-  <c r="H6" i="4" s="1"/>
-  <c r="G5" i="4"/>
-  <c r="H5" i="4" s="1"/>
-  <c r="G4" i="4"/>
-  <c r="H4" i="4" s="1"/>
-  <c r="G3" i="4"/>
-  <c r="H3" i="4" s="1"/>
-  <c r="G2" i="4"/>
-  <c r="H2" i="4" s="1"/>
-  <c r="G8" i="3"/>
-  <c r="H8" i="3" s="1"/>
-  <c r="G7" i="3"/>
-  <c r="H7" i="3" s="1"/>
-  <c r="G6" i="3"/>
-  <c r="H6" i="3" s="1"/>
-  <c r="G5" i="3"/>
-  <c r="H5" i="3" s="1"/>
-  <c r="G4" i="3"/>
-  <c r="H4" i="3" s="1"/>
-  <c r="G3" i="3"/>
-  <c r="H3" i="3" s="1"/>
-  <c r="G2" i="3"/>
-  <c r="H2" i="3" s="1"/>
-  <c r="G8" i="2"/>
-  <c r="H8" i="2" s="1"/>
-  <c r="G7" i="2"/>
-  <c r="H7" i="2" s="1"/>
-  <c r="G6" i="2"/>
-  <c r="H6" i="2" s="1"/>
-  <c r="G5" i="2"/>
-  <c r="H5" i="2" s="1"/>
-  <c r="G4" i="2"/>
-  <c r="H4" i="2" s="1"/>
-  <c r="G3" i="2"/>
-  <c r="H3" i="2" s="1"/>
-  <c r="G2" i="2"/>
-  <c r="H2" i="2" s="1"/>
-  <c r="G8" i="1"/>
-  <c r="H8" i="1" s="1"/>
-  <c r="G7" i="1"/>
-  <c r="H7" i="1" s="1"/>
-  <c r="H3" i="1"/>
-  <c r="H4" i="1"/>
-  <c r="H5" i="1"/>
-  <c r="H2" i="1"/>
-  <c r="G3" i="1"/>
-  <c r="G4" i="1"/>
-  <c r="G5" i="1"/>
-  <c r="G6" i="1"/>
-  <c r="H6" i="1" s="1"/>
-  <c r="G2" i="1"/>
-  <c r="H2" i="7"/>
-  <c r="H3" i="7"/>
-  <c r="H4" i="7"/>
-  <c r="H5" i="7"/>
-  <c r="H6" i="7"/>
-  <c r="H7" i="7"/>
-  <c r="H8" i="7"/>
-  <c r="I8" i="7" s="1"/>
-  <c r="I5" i="7"/>
-  <c r="I7" i="7"/>
-  <c r="I3" i="7"/>
-  <c r="I4" i="7"/>
-  <c r="I6" i="7"/>
-  <c r="I2" i="7"/>
-  <c r="G7" i="7"/>
-  <c r="G3" i="7"/>
-  <c r="G4" i="7"/>
-  <c r="G8" i="7"/>
-  <c r="G5" i="7"/>
-  <c r="G6" i="7"/>
-  <c r="G2" i="7"/>
-</calcChain>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="28">
   <si>
     <r>
@@ -404,11 +273,10 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -497,7 +365,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -569,21 +437,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -602,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -630,10 +483,10 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -669,7 +522,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -686,12 +539,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,7 +557,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1029,44 +876,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Documents\GitHub\fantasy-junino\assets\notas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1AC9C2-4644-42AB-92D4-7C852C0CBF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="TOTAL" sheetId="7" r:id="rId1"/>
-    <sheet name="COREOGRAFIA" sheetId="1" r:id="rId2"/>
-    <sheet name="MARCAÇÃO" sheetId="2" r:id="rId3"/>
-    <sheet name="ANIMAÇÃO" sheetId="3" r:id="rId4"/>
-    <sheet name="FIGURINOS" sheetId="4" r:id="rId5"/>
-    <sheet name="CASAL DE NOIVOS" sheetId="5" r:id="rId6"/>
-    <sheet name="TRILHA SONORA" sheetId="6" r:id="rId7"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADA6C8A-3A94-4B05-B614-F2A6DFEC3CBB}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="25" defaultRowHeight="12.75"/>
@@ -1121,13 +931,16 @@
         <v>895.1</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>298.36666666666667</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>59.673333333333332</v>
       </c>
       <c r="I2">
-        <f>H2/6</f>
+        <f t="shared" ref="I2:I8" si="2">H2/6</f>
+        <v>9.9455555555555559</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
@@ -1150,13 +963,16 @@
         <v>892.8</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>297.59999999999997</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>59.519999999999996</v>
       </c>
       <c r="I3">
-        <f>H3/6</f>
+        <f t="shared" si="2"/>
+        <v>9.92</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -1179,13 +995,16 @@
         <v>887</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>295.66666666666669</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>59.13333333333334</v>
       </c>
       <c r="I4">
-        <f>H4/6</f>
+        <f t="shared" si="2"/>
+        <v>9.8555555555555561</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -1208,13 +1027,16 @@
         <v>885.7</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>295.23333333333335</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>59.046666666666667</v>
       </c>
       <c r="I5">
-        <f>H5/6</f>
+        <f t="shared" si="2"/>
+        <v>9.8411111111111111</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1237,13 +1059,16 @@
         <v>874.6</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>291.53333333333336</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>58.306666666666672</v>
       </c>
       <c r="I6">
-        <f>H6/6</f>
+        <f t="shared" si="2"/>
+        <v>9.7177777777777781</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1266,13 +1091,16 @@
         <v>591.6</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>295.8</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>59.160000000000004</v>
       </c>
       <c r="I7">
-        <f>H7/6</f>
+        <f t="shared" si="2"/>
+        <v>9.8600000000000012</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1294,14 +1122,17 @@
       <c r="F8" s="4">
         <v>292.3</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>292.3</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>58.46</v>
       </c>
       <c r="I8">
-        <f>H8/6</f>
+        <f t="shared" si="2"/>
+        <v>9.7433333333333341</v>
       </c>
     </row>
   </sheetData>
@@ -1309,7 +1140,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -1365,10 +1196,12 @@
         <v>147.69999999999999</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>49.233333333333327</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>9.8466666666666658</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
@@ -1391,10 +1224,12 @@
         <v>147.4</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.133333333333333</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8266666666666662</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -1417,10 +1252,12 @@
         <v>145.69999999999999</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>48.566666666666663</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>9.7133333333333329</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -1443,10 +1280,12 @@
         <v>145.5</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>48.5</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
@@ -1469,10 +1308,12 @@
         <v>143.9</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>47.966666666666669</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>9.5933333333333337</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
@@ -1495,10 +1336,12 @@
         <v>97.7</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>48.85</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>9.77</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
@@ -1520,11 +1363,13 @@
       <c r="F8" s="10">
         <v>47.5</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>47.5</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1"/>
@@ -1543,7 +1388,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -1599,10 +1444,12 @@
         <v>149.5</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>49.833333333333336</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
@@ -1625,10 +1472,12 @@
         <v>148.4</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.466666666666669</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8933333333333344</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -1651,10 +1500,12 @@
         <v>148.19999999999999</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.4</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>9.879999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -1677,10 +1528,12 @@
         <v>147.80000000000001</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.266666666666673</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8533333333333353</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
@@ -1703,10 +1556,12 @@
         <v>145.6</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>48.533333333333331</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>9.706666666666667</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
@@ -1729,10 +1584,12 @@
         <v>97.7</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>48.85</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>9.77</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
@@ -1754,11 +1611,13 @@
       <c r="F8" s="10">
         <v>48.6</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>48.6</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>9.7200000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1"/>
@@ -1777,7 +1636,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -1833,10 +1692,12 @@
         <v>148.9</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>49.633333333333333</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>9.9266666666666659</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
@@ -1859,10 +1720,12 @@
         <v>148.5</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.5</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -1885,10 +1748,12 @@
         <v>147.9</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.300000000000004</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8600000000000012</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -1911,10 +1776,12 @@
         <v>146.9</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>48.966666666666669</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>9.793333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
@@ -1937,10 +1804,12 @@
         <v>145.4</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>48.466666666666669</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>9.6933333333333334</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
@@ -1963,10 +1832,12 @@
         <v>99.7</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>49.85</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9700000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
@@ -1988,11 +1859,13 @@
       <c r="F8" s="10">
         <v>49</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>49</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1"/>
@@ -2011,7 +1884,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -2067,10 +1940,12 @@
         <v>149.69999999999999</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>49.9</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>9.98</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
@@ -2093,10 +1968,12 @@
         <v>149.4</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.800000000000004</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9600000000000009</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -2119,10 +1996,12 @@
         <v>148.9</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.633333333333333</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9266666666666659</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -2145,10 +2024,12 @@
         <v>148.80000000000001</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.6</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>9.92</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
@@ -2171,10 +2052,12 @@
         <v>147.80000000000001</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.266666666666673</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8533333333333353</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
@@ -2197,10 +2080,12 @@
         <v>98.9</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>49.45</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>9.89</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
@@ -2222,11 +2107,13 @@
       <c r="F8" s="10">
         <v>48.8</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>48.8</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>9.76</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1"/>
@@ -2245,7 +2132,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -2301,10 +2188,12 @@
         <v>149.80000000000001</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>49.933333333333337</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>9.9866666666666681</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
@@ -2327,10 +2216,12 @@
         <v>149</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.666666666666664</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9333333333333336</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -2353,10 +2244,12 @@
         <v>148.1</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.366666666666667</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8733333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -2379,10 +2272,12 @@
         <v>147.80000000000001</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.266666666666673</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8533333333333353</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
@@ -2405,10 +2300,12 @@
         <v>145.1</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>48.366666666666667</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>9.6733333333333338</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
@@ -2431,10 +2328,12 @@
         <v>98.3</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>49.15</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>9.83</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
@@ -2456,11 +2355,13 @@
       <c r="F8" s="10">
         <v>48.4</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>48.4</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>9.68</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1"/>
@@ -2479,7 +2380,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -2535,10 +2436,12 @@
         <v>149.80000000000001</v>
       </c>
       <c r="G2">
-        <f>F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <f t="shared" ref="G2:G8" si="0">F2/COUNTIF(C2:E2,"&lt;&gt;0")</f>
+        <v>49.933333333333337</v>
       </c>
       <c r="H2">
-        <f>G2/5</f>
+        <f t="shared" ref="H2:H8" si="1">G2/5</f>
+        <v>9.9866666666666681</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
@@ -2559,10 +2462,12 @@
         <v>149.80000000000001</v>
       </c>
       <c r="G3">
-        <f>F3/COUNTIF(C3:E3,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.933333333333337</v>
       </c>
       <c r="H3">
-        <f>G3/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9866666666666681</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -2585,10 +2490,12 @@
         <v>149.5</v>
       </c>
       <c r="G4">
-        <f>F4/COUNTIF(C4:E4,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.833333333333336</v>
       </c>
       <c r="H4">
-        <f>G4/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9666666666666668</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
@@ -2611,10 +2518,12 @@
         <v>148.80000000000001</v>
       </c>
       <c r="G5">
-        <f>F5/COUNTIF(C5:E5,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.6</v>
       </c>
       <c r="H5">
-        <f>G5/5</f>
+        <f t="shared" si="1"/>
+        <v>9.92</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
@@ -2637,10 +2546,12 @@
         <v>148.4</v>
       </c>
       <c r="G6">
-        <f>F6/COUNTIF(C6:E6,"&lt;&gt;0")</f>
+        <f t="shared" si="0"/>
+        <v>49.466666666666669</v>
       </c>
       <c r="H6">
-        <f>G6/5</f>
+        <f t="shared" si="1"/>
+        <v>9.8933333333333344</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
@@ -2663,10 +2574,12 @@
         <v>99.5</v>
       </c>
       <c r="G7">
-        <f>F7/COUNTIF(C7:E7,"&lt;&gt;0")</f>
+        <f>F7/2</f>
+        <v>49.75</v>
       </c>
       <c r="H7">
-        <f>G7/5</f>
+        <f t="shared" si="1"/>
+        <v>9.9499999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
@@ -2688,11 +2601,13 @@
       <c r="F8" s="10">
         <v>50</v>
       </c>
-      <c r="G8">
-        <f>F8/COUNTIF(C8:E8,"&lt;&gt;0")</f>
+      <c r="G8" s="15">
+        <f>F8</f>
+        <v>50</v>
       </c>
       <c r="H8">
-        <f>G8/5</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1"/>
